--- a/ITU/ITUInfo.xlsx
+++ b/ITU/ITUInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\ITU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB25534-C69D-4BFB-85F9-F70247BE48DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A6B19E-6B3A-4584-8A5A-F9C3F2ED3A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,9 +88,6 @@
     <t>https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/course-plans.php?fakulte=IS</t>
   </si>
   <si>
-    <t>https://www.sis.itu.edu.tr/onkayitlar/lsyabanci/basvuru/index.php?islem=kontenjanlar-sartlar</t>
-  </si>
-  <si>
     <t>Quotas, Requirements and Descriptions</t>
   </si>
   <si>
@@ -98,6 +95,9 @@
   </si>
   <si>
     <t>https://www.itu.edu.tr/en/all-departments</t>
+  </si>
+  <si>
+    <t>https://www.sis.itu.edu.tr/onkayitlar/lsyabanci/basvuru/index.php?islem=kontenjanlar-sartlar&amp;program=TUMU</t>
   </si>
 </sst>
 </file>
@@ -622,7 +622,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="90.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -643,18 +643,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
         <v>12</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/ITU/ITUInfo.xlsx
+++ b/ITU/ITUInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\ITU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubNegar\University2\ITU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A6B19E-6B3A-4584-8A5A-F9C3F2ED3A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB16F52-C16B-41A7-8433-EED398C65A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42910" yWindow="5530" windowWidth="22980" windowHeight="11330" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>Faculty of Electrical and Electronics Engineering</t>
   </si>
@@ -98,6 +98,12 @@
   </si>
   <si>
     <t>https://www.sis.itu.edu.tr/onkayitlar/lsyabanci/basvuru/index.php?islem=kontenjanlar-sartlar&amp;program=TUMU</t>
+  </si>
+  <si>
+    <t>Intrnational Requirement</t>
+  </si>
+  <si>
+    <t>Undergraduate Applications of Candidates to be Accepted from Abroad quota for the 2024-2025 Academic Year (itu.edu.tr)</t>
   </si>
 </sst>
 </file>
@@ -533,13 +539,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="63.42578125" customWidth="1"/>
-    <col min="2" max="2" width="86.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="63.3984375" customWidth="1"/>
+    <col min="2" max="2" width="86.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,7 +556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -561,7 +567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -572,7 +578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -583,13 +589,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:3" s="6" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="9" spans="1:3" s="6" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="5" t="s">
         <v>2</v>
       </c>
@@ -600,7 +606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="6" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="6" customFormat="1" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7" t="s">
         <v>0</v>
       </c>
@@ -618,14 +624,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D281B26-88D0-4B07-911B-4BC1C12CD033}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="60.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="60.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -633,7 +639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -641,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -649,18 +655,28 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1" xr:uid="{5656C5A9-D6A8-4A1D-9E8A-CCDCF8192914}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{8EAAD1B9-EF9B-4720-BD4B-867AAB868575}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{AA40FC1F-6CA7-4BA6-AAEC-77FCC02BEB38}"/>
+    <hyperlink ref="B9" r:id="rId4" display="https://www.sis.itu.edu.tr/duyuru_ekler/yabanci/202510/EN/index.php" xr:uid="{FEEF6E48-A9DD-4733-8FC1-A0D3D5B88D6C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ITU/ITUInfo.xlsx
+++ b/ITU/ITUInfo.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubNegar\University2\ITU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\ITU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB16F52-C16B-41A7-8433-EED398C65A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829CC016-D7CA-4B93-B10C-904E48803BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42910" yWindow="5530" windowWidth="22980" windowHeight="11330" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Link" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Link" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
   <si>
     <t>Faculty of Electrical and Electronics Engineering</t>
   </si>
@@ -104,6 +105,39 @@
   </si>
   <si>
     <t>Undergraduate Applications of Candidates to be Accepted from Abroad quota for the 2024-2025 Academic Year (itu.edu.tr)</t>
+  </si>
+  <si>
+    <t>https://www.itu.edu.tr/en/programs</t>
+  </si>
+  <si>
+    <t>programs</t>
+  </si>
+  <si>
+    <t>Faculty of Management</t>
+  </si>
+  <si>
+    <t>Management Engineering (%100 English)</t>
+  </si>
+  <si>
+    <t>Faculty of Aeronautics and Astronautics</t>
+  </si>
+  <si>
+    <t>Astronautical Engineering (%100 English)</t>
+  </si>
+  <si>
+    <t>Faculty of Science and Letters</t>
+  </si>
+  <si>
+    <t>Molecular Biology and Genetics (%100 English)</t>
+  </si>
+  <si>
+    <t>Faculty of Mines</t>
+  </si>
+  <si>
+    <t>Petroleum and Natural Gas Engineering (%100 English)</t>
+  </si>
+  <si>
+    <t>Economics (% 100 English)</t>
   </si>
 </sst>
 </file>
@@ -538,83 +572,208 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="63.3984375" customWidth="1"/>
-    <col min="2" max="2" width="86.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="63.42578125" customWidth="1"/>
+    <col min="2" max="2" width="86.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
         <v>2</v>
       </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:3" s="6" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="6" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B2FBDF-8B53-409C-B694-7F2EF8C8BEDD}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3">
         <v>3</v>
       </c>
-      <c r="C3">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="9" spans="1:3" s="6" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="5" t="s">
+      <c r="C7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" s="6" customFormat="1" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="7">
-        <v>10</v>
+      <c r="C8">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -622,16 +781,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D281B26-88D0-4B07-911B-4BC1C12CD033}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -639,7 +798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -647,7 +806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -655,7 +814,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>13</v>
       </c>
@@ -663,12 +822,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/ITU/ITUInfo.xlsx
+++ b/ITU/ITUInfo.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\ITU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829CC016-D7CA-4B93-B10C-904E48803BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E1C663-1BFC-4949-9396-7614006E0814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Link" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -844,7 +845,17 @@
     <hyperlink ref="B3" r:id="rId2" xr:uid="{8EAAD1B9-EF9B-4720-BD4B-867AAB868575}"/>
     <hyperlink ref="B5" r:id="rId3" xr:uid="{AA40FC1F-6CA7-4BA6-AAEC-77FCC02BEB38}"/>
     <hyperlink ref="B9" r:id="rId4" display="https://www.sis.itu.edu.tr/duyuru_ekler/yabanci/202510/EN/index.php" xr:uid="{FEEF6E48-A9DD-4733-8FC1-A0D3D5B88D6C}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{6D5D40FD-385B-4AE8-8732-7DFA6FE38445}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29310C1D-A8ED-4D89-9275-C963E10C7ED1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ITU/ITUInfo.xlsx
+++ b/ITU/ITUInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\ITU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E1C663-1BFC-4949-9396-7614006E0814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188DD29A-F6E3-4E8D-9222-D5ACB7E794B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>Faculty of Electrical and Electronics Engineering</t>
   </si>
@@ -139,6 +139,30 @@
   </si>
   <si>
     <t>Economics (% 100 English)</t>
+  </si>
+  <si>
+    <t>BEYLİKDÜZÜ KAVAKLI</t>
+  </si>
+  <si>
+    <t>20min</t>
+  </si>
+  <si>
+    <t>walk</t>
+  </si>
+  <si>
+    <t>25min</t>
+  </si>
+  <si>
+    <t>BEYLİKDÜZÜ YAKUPLU</t>
+  </si>
+  <si>
+    <t>32min</t>
+  </si>
+  <si>
+    <t>BEYLİKDÜZÜ ZÜBEYDE ANA YAŞAM MERKEZİ</t>
+  </si>
+  <si>
+    <t>bee</t>
   </si>
 </sst>
 </file>
@@ -853,9 +877,52 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29310C1D-A8ED-4D89-9275-C963E10C7ED1}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>